--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N68_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N68_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.18862978081535</v>
+        <v>1.168152339382494</v>
       </c>
       <c r="D2" t="n">
-        <v>7.185941619887711</v>
+        <v>1.167715513231753</v>
       </c>
       <c r="E2" t="n">
-        <v>10.49730985197387</v>
+        <v>1.705812850945754</v>
       </c>
       <c r="F2" t="n">
-        <v>3.289204597193783</v>
+        <v>0.5344957470439897</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>21.82852472931563</v>
+        <v>3.54713526851379</v>
       </c>
       <c r="D3" t="n">
-        <v>10.11554831588272</v>
+        <v>1.643776601330942</v>
       </c>
       <c r="E3" t="n">
-        <v>10.49730985197387</v>
+        <v>1.705812850945754</v>
       </c>
       <c r="F3" t="n">
-        <v>3.289204597193783</v>
+        <v>0.5344957470439897</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>19.35990093883622</v>
+        <v>3.145983902560886</v>
       </c>
       <c r="D4" t="n">
-        <v>11.24298340435786</v>
+        <v>1.826984803208152</v>
       </c>
       <c r="E4" t="n">
-        <v>10.49730985197387</v>
+        <v>1.705812850945754</v>
       </c>
       <c r="F4" t="n">
-        <v>3.289204597193783</v>
+        <v>0.5344957470439897</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>1.785151677855404</v>
+        <v>0.2900871476515031</v>
       </c>
       <c r="D5" t="n">
-        <v>2.296683313749575</v>
+        <v>0.3732110384843059</v>
       </c>
       <c r="E5" t="n">
-        <v>10.49730985197387</v>
+        <v>1.705812850945754</v>
       </c>
       <c r="F5" t="n">
-        <v>3.289204597193783</v>
+        <v>0.5344957470439897</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.04311598716886</v>
+        <v>5.044506347914941</v>
       </c>
       <c r="D6" t="n">
-        <v>10.50471790172443</v>
+        <v>1.707016659030221</v>
       </c>
       <c r="E6" t="n">
-        <v>10.49730985197387</v>
+        <v>1.705812850945754</v>
       </c>
       <c r="F6" t="n">
-        <v>3.289204597193783</v>
+        <v>0.5344957470439897</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
